--- a/samples/Sample_4_For_School_Class_Teacher.xlsx
+++ b/samples/Sample_4_For_School_Class_Teacher.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yash Shetty</t>
+          <t>Devansh Shetty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pooja Murthy</t>
+          <t>Aadhya Kumar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Karthik Kulkarni</t>
+          <t>Krishna Sharma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Neha Kumar</t>
+          <t>Riya Shetty</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Siddharth Bhat</t>
+          <t>Rohan Iyer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ishita Hegde</t>
+          <t>Sneha Patel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arjun Singh</t>
+          <t>Akash Hegde</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aadhya Iyer</t>
+          <t>Swathi Hegde</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Varun Murthy</t>
+          <t>Vihaan Kumar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Priya Gowda</t>
+          <t>Tanya Patel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sameer Iyer</t>
+          <t>Nikhil Desai</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shreya Prabhu</t>
+          <t>Ananya Singh</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aditya Desai</t>
+          <t>Arjun Bhat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Meera Hegde</t>
+          <t>Pooja Hegde</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Karthik Joshi</t>
+          <t>Vikram Verma</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shreya Rao</t>
+          <t>Riya Kulkarni</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vivaan Shetty</t>
+          <t>Vihaan Naik</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sara Joshi</t>
+          <t>Riya Naik</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aarav Hegde</t>
+          <t>Rahul Sharma</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pooja Joshi</t>
+          <t>Myra Desai</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rahul Verma</t>
+          <t>Nikhil Sharma</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Anjali Verma</t>
+          <t>Shreya Prabhu</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Varun Pai</t>
+          <t>Yash Patel</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sara Pai</t>
+          <t>Kavya Iyer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Devansh Kumar</t>
+          <t>Vihaan Pai</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aadhya Naik</t>
+          <t>Sneha Kumar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aditya Nair</t>
+          <t>Sameer Singh</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sneha Reddy</t>
+          <t>Sara Iyer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rahul Singh</t>
+          <t>Varun Shetty</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Divya Joshi</t>
+          <t>Neha Desai</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1615,24 +1615,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
         <v>47</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ratio &amp; Proportion</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -1642,33 +1646,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ratio &amp; Proportion</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
-        </is>
-      </c>
+          <t>Perimeter &amp; Area</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1677,33 +1677,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
         <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Ratio &amp; Proportion</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1712,24 +1704,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" t="n">
         <v>34</v>
       </c>
-      <c r="E5" t="n">
-        <v>33</v>
-      </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Simple Equations</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1739,16 +1735,16 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C6" t="n">
         <v>27</v>
-      </c>
-      <c r="C6" t="n">
-        <v>29</v>
       </c>
       <c r="D6" t="n">
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" t="n">
         <v>30</v>
@@ -1761,11 +1757,7 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>On track, but should aim higher with focused practice.</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1777,13 +1769,13 @@
         <v>29</v>
       </c>
       <c r="C7" t="n">
+        <v>29</v>
+      </c>
+      <c r="D7" t="n">
         <v>31</v>
       </c>
-      <c r="D7" t="n">
-        <v>30</v>
-      </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
         <v>27</v>
@@ -1791,7 +1783,11 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Perimeter &amp; Area</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1801,26 +1797,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Simple Equations</t>
+          <t>Ratio &amp; Proportion</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1832,19 +1828,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1859,24 +1855,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Simple Equations</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1886,26 +1886,26 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
+          <t>Fractions &amp; Decimals</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1917,22 +1917,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="n">
         <v>38</v>
       </c>
       <c r="D12" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" t="n">
         <v>42</v>
       </c>
-      <c r="E12" t="n">
-        <v>39</v>
-      </c>
-      <c r="F12" t="n">
-        <v>37</v>
-      </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -1944,26 +1944,26 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E13" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
+          <t>Perimeter &amp; Area</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1975,16 +1975,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
         <v>46</v>
@@ -1992,16 +1992,8 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Simple Equations</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Exceptional performance, keep up this standard.</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2010,13 +2002,13 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>39</v>
+      </c>
+      <c r="C15" t="n">
         <v>41</v>
       </c>
-      <c r="C15" t="n">
-        <v>42</v>
-      </c>
       <c r="D15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E15" t="n">
         <v>41</v>
@@ -2040,25 +2032,21 @@
         <v>43</v>
       </c>
       <c r="C16" t="n">
+        <v>43</v>
+      </c>
+      <c r="D16" t="n">
         <v>41</v>
-      </c>
-      <c r="D16" t="n">
-        <v>43</v>
       </c>
       <c r="E16" t="n">
         <v>44</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Perimeter &amp; Area</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -2068,33 +2056,29 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
+        <v>28</v>
+      </c>
+      <c r="D17" t="n">
         <v>29</v>
       </c>
-      <c r="D17" t="n">
-        <v>31</v>
-      </c>
       <c r="E17" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Simple Equations</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2103,33 +2087,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
+        <v>34</v>
+      </c>
+      <c r="E18" t="n">
+        <v>34</v>
+      </c>
+      <c r="F18" t="n">
         <v>31</v>
       </c>
-      <c r="E18" t="n">
-        <v>32</v>
-      </c>
-      <c r="F18" t="n">
-        <v>32</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Lines &amp; Angles</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Average performance — revision of basics recommended.</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2138,16 +2114,16 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>33</v>
+      </c>
+      <c r="C19" t="n">
         <v>28</v>
       </c>
-      <c r="C19" t="n">
-        <v>32</v>
-      </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F19" t="n">
         <v>32</v>
@@ -2155,12 +2131,12 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Average performance — revision of basics recommended.</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Perimeter &amp; Area</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2172,16 +2148,16 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F20" t="n">
         <v>20</v>
-      </c>
-      <c r="D20" t="n">
-        <v>22</v>
-      </c>
-      <c r="E20" t="n">
-        <v>21</v>
-      </c>
-      <c r="F20" t="n">
-        <v>18</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2196,29 +2172,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2227,31 +2199,27 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>14</v>
+      </c>
+      <c r="C22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" t="n">
         <v>10</v>
       </c>
-      <c r="C22" t="n">
-        <v>11</v>
-      </c>
-      <c r="D22" t="n">
-        <v>11</v>
-      </c>
-      <c r="E22" t="n">
-        <v>10</v>
-      </c>
-      <c r="F22" t="n">
-        <v>14</v>
-      </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Fractions &amp; Decimals</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Serious concern — immediate intervention needed.</t>
+          <t>Very low scores across the board, please involve parents.</t>
         </is>
       </c>
     </row>
@@ -2262,25 +2230,33 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Fractions &amp; Decimals</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Great turnaround this term, keep the momentum going!</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2289,28 +2265,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E24" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Lines &amp; Angles</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2320,25 +2292,33 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Fractions &amp; Decimals</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Inconsistent results — strong in some tests, weak in others.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2347,24 +2327,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C26" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D26" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Ratio &amp; Proportion</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2374,28 +2358,24 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>42</v>
+      </c>
+      <c r="C27" t="n">
         <v>40</v>
       </c>
-      <c r="C27" t="n">
-        <v>44</v>
-      </c>
       <c r="D27" t="n">
+        <v>41</v>
+      </c>
+      <c r="E27" t="n">
         <v>42</v>
       </c>
-      <c r="E27" t="n">
-        <v>40</v>
-      </c>
       <c r="F27" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Simple Equations</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2405,16 +2385,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C28" t="n">
+        <v>42</v>
+      </c>
+      <c r="D28" t="n">
+        <v>44</v>
+      </c>
+      <c r="E28" t="n">
         <v>43</v>
-      </c>
-      <c r="D28" t="n">
-        <v>42</v>
-      </c>
-      <c r="E28" t="n">
-        <v>41</v>
       </c>
       <c r="F28" t="n">
         <v>43</v>
@@ -2424,7 +2404,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Perimeter &amp; Area</t>
+          <t>Fractions &amp; Decimals</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -2436,19 +2416,19 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>29</v>
+      </c>
+      <c r="C29" t="n">
+        <v>29</v>
+      </c>
+      <c r="D29" t="n">
+        <v>28</v>
+      </c>
+      <c r="E29" t="n">
+        <v>30</v>
+      </c>
+      <c r="F29" t="n">
         <v>27</v>
-      </c>
-      <c r="C29" t="n">
-        <v>31</v>
-      </c>
-      <c r="D29" t="n">
-        <v>27</v>
-      </c>
-      <c r="E29" t="n">
-        <v>32</v>
-      </c>
-      <c r="F29" t="n">
-        <v>31</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2467,29 +2447,33 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="n">
+        <v>28</v>
+      </c>
+      <c r="D30" t="n">
         <v>25</v>
       </c>
-      <c r="C30" t="n">
-        <v>27</v>
-      </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" t="n">
         <v>30</v>
       </c>
-      <c r="E30" t="n">
-        <v>30</v>
-      </c>
-      <c r="F30" t="n">
-        <v>28</v>
-      </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Simple Equations</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Average performance — revision of basics recommended.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2498,19 +2482,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D31" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F31" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2601,26 +2585,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D2" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E2" t="n">
         <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Acids Bases &amp; Salts</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -2632,33 +2616,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2667,29 +2643,33 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Heat</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Nutrition in Plants</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Strong performer, small gains possible with more practice.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2698,19 +2678,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
+        <v>61</v>
+      </c>
+      <c r="D5" t="n">
         <v>55</v>
       </c>
-      <c r="D5" t="n">
-        <v>53</v>
-      </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -2725,26 +2705,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Acids Bases &amp; Salts</t>
+          <t>Weather &amp; Climate</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2756,26 +2736,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C7" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D7" t="n">
         <v>54</v>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Nutrition in Plants</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2787,31 +2767,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
+          <t>Motion &amp; Time</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -2822,28 +2802,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Nutrition in Plants</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -2853,29 +2829,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F10" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Needs urgent academic support, at risk of failing.</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2884,24 +2856,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -2911,26 +2887,26 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E12" t="n">
         <v>61</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Weather &amp; Climate</t>
+          <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2942,19 +2918,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2969,19 +2945,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C14" t="n">
         <v>98</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E14" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F14" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -2996,16 +2972,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F15" t="n">
         <v>76</v>
@@ -3013,7 +2989,11 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Nutrition in Plants</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -3023,33 +3003,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C16" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D16" t="n">
+        <v>85</v>
+      </c>
+      <c r="E16" t="n">
+        <v>82</v>
+      </c>
+      <c r="F16" t="n">
         <v>83</v>
       </c>
-      <c r="E16" t="n">
-        <v>84</v>
-      </c>
-      <c r="F16" t="n">
-        <v>84</v>
-      </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Strong performer, small gains possible with more practice.</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3058,24 +3030,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F17" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -3085,26 +3061,26 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C18" t="n">
+        <v>62</v>
+      </c>
+      <c r="D18" t="n">
+        <v>70</v>
+      </c>
+      <c r="E18" t="n">
+        <v>63</v>
+      </c>
+      <c r="F18" t="n">
         <v>65</v>
       </c>
-      <c r="D18" t="n">
-        <v>61</v>
-      </c>
-      <c r="E18" t="n">
-        <v>70</v>
-      </c>
-      <c r="F18" t="n">
-        <v>68</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Acids Bases &amp; Salts</t>
+          <t>Motion &amp; Time</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -3116,26 +3092,26 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>65</v>
+      </c>
+      <c r="C19" t="n">
+        <v>59</v>
+      </c>
+      <c r="D19" t="n">
         <v>64</v>
       </c>
-      <c r="C19" t="n">
-        <v>63</v>
-      </c>
-      <c r="D19" t="n">
-        <v>65</v>
-      </c>
       <c r="E19" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Weather &amp; Climate</t>
+          <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3147,26 +3123,26 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>34</v>
+      </c>
+      <c r="C20" t="n">
         <v>32</v>
       </c>
-      <c r="C20" t="n">
-        <v>38</v>
-      </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E20" t="n">
         <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Motion &amp; Time</t>
+          <t>Nutrition in Plants</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3178,33 +3154,29 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C21" t="n">
+        <v>34</v>
+      </c>
+      <c r="D21" t="n">
         <v>42</v>
       </c>
-      <c r="D21" t="n">
-        <v>47</v>
-      </c>
       <c r="E21" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Acids Bases &amp; Salts</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
-        </is>
-      </c>
+          <t>Motion &amp; Time</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3213,33 +3185,29 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" t="n">
         <v>15</v>
       </c>
-      <c r="E22" t="n">
-        <v>14</v>
-      </c>
       <c r="F22" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Needs urgent academic support, at risk of failing.</t>
-        </is>
-      </c>
+          <t>Heat</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3248,28 +3216,24 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>50</v>
+      </c>
+      <c r="C23" t="n">
         <v>56</v>
       </c>
-      <c r="C23" t="n">
-        <v>55</v>
-      </c>
       <c r="D23" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E23" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F23" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Motion &amp; Time</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -3279,33 +3243,29 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C24" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F24" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Noticeable drop in performance, please check in at home.</t>
-        </is>
-      </c>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3314,29 +3274,33 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C25" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E25" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F25" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Ups and downs need to be understood — talk to student directly.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3345,26 +3309,26 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D26" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E26" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F26" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
+          <t>Motion &amp; Time</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3376,26 +3340,26 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D27" t="n">
+        <v>82</v>
+      </c>
+      <c r="E27" t="n">
         <v>73</v>
       </c>
-      <c r="E27" t="n">
-        <v>75</v>
-      </c>
       <c r="F27" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Acids Bases &amp; Salts</t>
+          <t>Weather &amp; Climate</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3407,29 +3371,29 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>74</v>
+      </c>
+      <c r="C28" t="n">
+        <v>83</v>
+      </c>
+      <c r="D28" t="n">
+        <v>75</v>
+      </c>
+      <c r="E28" t="n">
         <v>79</v>
       </c>
-      <c r="C28" t="n">
-        <v>89</v>
-      </c>
-      <c r="D28" t="n">
-        <v>83</v>
-      </c>
-      <c r="E28" t="n">
-        <v>82</v>
-      </c>
       <c r="F28" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Nutrition in Plants</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Solid understanding, encourage attempting harder problems.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3438,24 +3402,28 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>53</v>
+      </c>
+      <c r="C29" t="n">
+        <v>61</v>
+      </c>
+      <c r="D29" t="n">
         <v>55</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
+        <v>50</v>
+      </c>
+      <c r="F29" t="n">
         <v>53</v>
       </c>
-      <c r="D29" t="n">
-        <v>60</v>
-      </c>
-      <c r="E29" t="n">
-        <v>53</v>
-      </c>
-      <c r="F29" t="n">
-        <v>61</v>
-      </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -3465,10 +3433,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C30" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D30" t="n">
         <v>54</v>
@@ -3477,17 +3445,13 @@
         <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Average performance — revision of basics recommended.</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3496,19 +3460,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C31" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F31" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -3520,7 +3484,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -3606,13 +3570,13 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
         <v>49</v>
@@ -3622,14 +3586,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The Ant and the Cricket (Poem)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
-        </is>
-      </c>
+          <t>Reading Comprehension</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3638,31 +3598,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
+        <v>44</v>
+      </c>
+      <c r="D3" t="n">
         <v>42</v>
       </c>
-      <c r="D3" t="n">
-        <v>40</v>
-      </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Letter Writing</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Solid understanding, encourage attempting harder problems.</t>
         </is>
       </c>
     </row>
@@ -3673,24 +3629,28 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>43</v>
+      </c>
+      <c r="C4" t="n">
         <v>41</v>
       </c>
-      <c r="C4" t="n">
-        <v>42</v>
-      </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="n">
         <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Reading Comprehension</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -3700,29 +3660,29 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
         <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Average performance — revision of basics recommended.</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>The Ant and the Cricket (Poem)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3731,28 +3691,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
         <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>The Ant and the Cricket (Poem)</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -3762,20 +3718,20 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>29</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27</v>
+      </c>
+      <c r="E7" t="n">
+        <v>28</v>
+      </c>
+      <c r="F7" t="n">
         <v>30</v>
       </c>
-      <c r="C7" t="n">
-        <v>28</v>
-      </c>
-      <c r="D7" t="n">
-        <v>31</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30</v>
-      </c>
-      <c r="F7" t="n">
-        <v>32</v>
-      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
@@ -3784,7 +3740,11 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Steady but needs more consistency across topics.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3793,24 +3753,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
+        <v>21</v>
+      </c>
+      <c r="D8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" t="n">
         <v>19</v>
       </c>
-      <c r="D8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E8" t="n">
-        <v>18</v>
-      </c>
-      <c r="F8" t="n">
-        <v>15</v>
-      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>The Ant and the Cricket (Poem)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -3826,23 +3790,27 @@
         <v>23</v>
       </c>
       <c r="D9" t="n">
+        <v>19</v>
+      </c>
+      <c r="E9" t="n">
+        <v>19</v>
+      </c>
+      <c r="F9" t="n">
         <v>22</v>
       </c>
-      <c r="E9" t="n">
-        <v>24</v>
-      </c>
-      <c r="F9" t="n">
-        <v>20</v>
-      </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The Ant and the Cricket (Poem)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3851,26 +3819,26 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>The Ant and the Cricket (Poem)</t>
+          <t>Reading Comprehension</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -3882,25 +3850,29 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
+        <v>34</v>
+      </c>
+      <c r="F11" t="n">
         <v>32</v>
       </c>
-      <c r="F11" t="n">
-        <v>31</v>
-      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Visible improvement — the extra effort is showing results.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3909,29 +3881,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Needs attention — performance has slipped recently.</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3940,19 +3908,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -3971,33 +3939,29 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>49</v>
+      </c>
+      <c r="C14" t="n">
         <v>46</v>
       </c>
-      <c r="C14" t="n">
-        <v>43</v>
-      </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Grammar - Tenses</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
-        </is>
-      </c>
+          <t>The Ant and the Cricket (Poem)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4006,16 +3970,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" t="n">
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F15" t="n">
         <v>41</v>
@@ -4025,7 +3989,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>The Ant and the Cricket (Poem)</t>
+          <t>Grammar - Tenses</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -4037,29 +4001,29 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>45</v>
+      </c>
+      <c r="C16" t="n">
+        <v>44</v>
+      </c>
+      <c r="D16" t="n">
+        <v>41</v>
+      </c>
+      <c r="E16" t="n">
         <v>42</v>
       </c>
-      <c r="C16" t="n">
-        <v>40</v>
-      </c>
-      <c r="D16" t="n">
-        <v>40</v>
-      </c>
-      <c r="E16" t="n">
-        <v>43</v>
-      </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Letter Writing</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Solid understanding, encourage attempting harder problems.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4068,19 +4032,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E17" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -4102,16 +4066,16 @@
         <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E18" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -4123,7 +4087,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -4134,29 +4098,29 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>28</v>
+      </c>
+      <c r="C19" t="n">
         <v>31</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>28</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>27</v>
       </c>
-      <c r="E19" t="n">
-        <v>31</v>
-      </c>
       <c r="F19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Letter Writing</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>On track, but should aim higher with focused practice.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4165,28 +4129,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>The Ant and the Cricket (Poem)</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -4196,24 +4156,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -4223,26 +4187,26 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
         <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Grammar - Tenses</t>
+          <t>Letter Writing</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -4254,24 +4218,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E23" t="n">
+        <v>33</v>
+      </c>
+      <c r="F23" t="n">
         <v>35</v>
       </c>
-      <c r="F23" t="n">
-        <v>33</v>
-      </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -4281,19 +4249,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D24" t="n">
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -4303,11 +4271,7 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Was doing well earlier, something seems to be affecting focus now.</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4316,19 +4280,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D25" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F25" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -4347,33 +4311,29 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>49</v>
+      </c>
+      <c r="C26" t="n">
         <v>45</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
+        <v>45</v>
+      </c>
+      <c r="E26" t="n">
+        <v>45</v>
+      </c>
+      <c r="F26" t="n">
         <v>48</v>
       </c>
-      <c r="D26" t="n">
-        <v>48</v>
-      </c>
-      <c r="E26" t="n">
-        <v>47</v>
-      </c>
-      <c r="F26" t="n">
-        <v>46</v>
-      </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Grammar - Tenses</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Consistently excellent — ready for tougher challenges.</t>
-        </is>
-      </c>
+          <t>Reading Comprehension</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4382,26 +4342,26 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C27" t="n">
         <v>38</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E27" t="n">
         <v>38</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>The Ant and the Cricket (Poem)</t>
+          <t>Grammar - Tenses</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4413,24 +4373,28 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>39</v>
+      </c>
+      <c r="C28" t="n">
+        <v>41</v>
+      </c>
+      <c r="D28" t="n">
+        <v>41</v>
+      </c>
+      <c r="E28" t="n">
+        <v>38</v>
+      </c>
+      <c r="F28" t="n">
         <v>37</v>
       </c>
-      <c r="C28" t="n">
-        <v>36</v>
-      </c>
-      <c r="D28" t="n">
-        <v>40</v>
-      </c>
-      <c r="E28" t="n">
-        <v>37</v>
-      </c>
-      <c r="F28" t="n">
-        <v>42</v>
-      </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -4443,26 +4407,26 @@
         <v>31</v>
       </c>
       <c r="C29" t="n">
+        <v>31</v>
+      </c>
+      <c r="D29" t="n">
+        <v>28</v>
+      </c>
+      <c r="E29" t="n">
         <v>29</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>31</v>
       </c>
-      <c r="E29" t="n">
-        <v>30</v>
-      </c>
-      <c r="F29" t="n">
-        <v>32</v>
-      </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Grammar - Tenses</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Average performance — revision of basics recommended.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4471,16 +4435,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D30" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E30" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F30" t="n">
         <v>27</v>
@@ -4490,10 +4454,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>The Ant and the Cricket (Poem)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Steady but needs more consistency across topics.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4502,26 +4470,26 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F31" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Letter Writing</t>
+          <t>Grammar - Tenses</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4605,28 +4573,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C2" t="n">
+        <v>84</v>
+      </c>
+      <c r="D2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E2" t="n">
         <v>92</v>
       </c>
-      <c r="D2" t="n">
-        <v>91</v>
-      </c>
-      <c r="E2" t="n">
-        <v>94</v>
-      </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Gadya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
@@ -4640,24 +4604,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>Strong performer, small gains possible with more practice.</t>
@@ -4671,31 +4639,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
+          <t>Solid understanding, encourage attempting harder problems.</t>
         </is>
       </c>
     </row>
@@ -4706,26 +4674,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C5" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Gadya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4741,27 +4709,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
         <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -4772,31 +4744,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D7" t="n">
+        <v>53</v>
+      </c>
+      <c r="E7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F7" t="n">
         <v>51</v>
       </c>
-      <c r="E7" t="n">
-        <v>60</v>
-      </c>
-      <c r="F7" t="n">
-        <v>55</v>
-      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Gadya Pathya 1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -4807,27 +4779,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
+        <v>33</v>
+      </c>
+      <c r="D8" t="n">
+        <v>32</v>
+      </c>
+      <c r="E8" t="n">
         <v>35</v>
       </c>
-      <c r="D8" t="n">
-        <v>35</v>
-      </c>
-      <c r="E8" t="n">
-        <v>30</v>
-      </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Gadya Pathya 1</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
+          <t>Struggling with fundamentals, needs remedial sessions.</t>
         </is>
       </c>
     </row>
@@ -4838,27 +4814,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -4869,19 +4849,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4904,19 +4884,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C11" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D11" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="F11" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4924,7 +4904,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Encouraging progress, on the right track now.</t>
+          <t>Great turnaround this term, keep the momentum going!</t>
         </is>
       </c>
     </row>
@@ -4935,31 +4915,27 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Padya Pathya 1</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Was doing well earlier, something seems to be affecting focus now.</t>
+          <t>Noticeable drop in performance, please check in at home.</t>
         </is>
       </c>
     </row>
@@ -4970,19 +4946,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -4994,7 +4970,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Unpredictable performance, may help to identify what's different on good days.</t>
+          <t>Ups and downs need to be understood — talk to student directly.</t>
         </is>
       </c>
     </row>
@@ -5005,31 +4981,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="n">
+        <v>98</v>
+      </c>
+      <c r="E14" t="n">
+        <v>93</v>
+      </c>
+      <c r="F14" t="n">
         <v>97</v>
       </c>
-      <c r="D14" t="n">
-        <v>93</v>
-      </c>
-      <c r="E14" t="n">
-        <v>90</v>
-      </c>
-      <c r="F14" t="n">
-        <v>89</v>
-      </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
+          <t>Consistently excellent — ready for tougher challenges.</t>
         </is>
       </c>
     </row>
@@ -5040,19 +5016,19 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>81</v>
+      </c>
+      <c r="C15" t="n">
         <v>88</v>
       </c>
-      <c r="C15" t="n">
-        <v>87</v>
-      </c>
       <c r="D15" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E15" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F15" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -5060,7 +5036,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -5071,16 +5047,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C16" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F16" t="n">
         <v>82</v>
@@ -5088,7 +5064,11 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>Doing very well overall, minor slips in application-based questions.</t>
@@ -5102,31 +5082,27 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E17" t="n">
         <v>60</v>
       </c>
       <c r="F17" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Gadya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -5137,31 +5113,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C18" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E18" t="n">
         <v>63</v>
       </c>
       <c r="F18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -5172,16 +5148,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C19" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E19" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F19" t="n">
         <v>64</v>
@@ -5191,7 +5167,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Gadya Pathya 1</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5207,27 +5183,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C20" t="n">
+        <v>39</v>
+      </c>
+      <c r="D20" t="n">
         <v>35</v>
       </c>
-      <c r="D20" t="n">
-        <v>25</v>
-      </c>
       <c r="E20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F20" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -5238,31 +5218,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C21" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D21" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E21" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
+          <t>Struggling with fundamentals, needs remedial sessions.</t>
         </is>
       </c>
     </row>
@@ -5273,31 +5253,31 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>25</v>
+      </c>
+      <c r="C22" t="n">
+        <v>22</v>
+      </c>
+      <c r="D22" t="n">
         <v>23</v>
       </c>
-      <c r="C22" t="n">
-        <v>28</v>
-      </c>
-      <c r="D22" t="n">
-        <v>31</v>
-      </c>
       <c r="E22" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Needs urgent academic support, at risk of failing.</t>
+          <t>Very low scores across the board, please involve parents.</t>
         </is>
       </c>
     </row>
@@ -5308,31 +5288,31 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>90</v>
+      </c>
+      <c r="C23" t="n">
         <v>83</v>
       </c>
-      <c r="C23" t="n">
-        <v>80</v>
-      </c>
       <c r="D23" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E23" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F23" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Gadya Pathya 1</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Great turnaround this term, keep the momentum going!</t>
+          <t>Encouraging progress, on the right track now.</t>
         </is>
       </c>
     </row>
@@ -5343,31 +5323,27 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C24" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Vyakarana Basics</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Was doing well earlier, something seems to be affecting focus now.</t>
+          <t>Noticeable drop in performance, please check in at home.</t>
         </is>
       </c>
     </row>
@@ -5378,31 +5354,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E25" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F25" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Gadya Pathya 1</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ups and downs need to be understood — talk to student directly.</t>
+          <t>Unpredictable performance, may help to identify what's different on good days.</t>
         </is>
       </c>
     </row>
@@ -5416,24 +5392,28 @@
         <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D26" t="n">
         <v>100</v>
       </c>
       <c r="E26" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F26" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Gadya Pathya 1</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
+          <t>Consistently excellent — ready for tougher challenges.</t>
         </is>
       </c>
     </row>
@@ -5444,31 +5424,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C27" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D27" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E27" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F27" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Gadya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
+          <t>Strong performer, small gains possible with more practice.</t>
         </is>
       </c>
     </row>
@@ -5479,24 +5459,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C28" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D28" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E28" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F28" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>Strong performer, small gains possible with more practice.</t>
@@ -5510,16 +5494,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C29" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D29" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E29" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F29" t="n">
         <v>61</v>
@@ -5527,14 +5511,10 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Padya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -5545,31 +5525,27 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F30" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Vyakarana Basics</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -5580,26 +5556,26 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C31" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D31" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E31" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F31" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Gadya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">

--- a/samples/Sample_4_For_School_Class_Teacher.xlsx
+++ b/samples/Sample_4_For_School_Class_Teacher.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SETUP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Test 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mid-Term" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Test 2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Exam" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7A-Unit Test 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7A-Mid-Term" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7A-Unit Test 2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7A-Final Exam" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -637,7 +637,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unit Test 1</t>
+          <t>Class7A-Unit Test 1</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mid-Term</t>
+          <t>Class7A-Mid-Term</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unit Test 2</t>
+          <t>Class7A-Unit Test 2</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Final Exam</t>
+          <t>Class7A-Final Exam</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,6 @@
           <t>Ratio &amp; Proportion</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1668,7 +1667,6 @@
           <t>Perimeter &amp; Area</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1694,8 +1692,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1726,7 +1722,6 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1757,7 +1752,6 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1788,7 +1782,6 @@
           <t>Perimeter &amp; Area</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1819,7 +1812,6 @@
           <t>Ratio &amp; Proportion</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1845,8 +1837,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1877,7 +1867,6 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1908,7 +1897,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1934,8 +1922,6 @@
       <c r="G12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1966,7 +1952,6 @@
           <t>Perimeter &amp; Area</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1992,8 +1977,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2019,8 +2002,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2046,8 +2027,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2078,7 +2057,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2104,8 +2082,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2136,7 +2112,6 @@
           <t>Perimeter &amp; Area</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2162,8 +2137,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2189,8 +2162,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2216,7 +2187,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Very low scores across the board, please involve parents.</t>
@@ -2282,8 +2252,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2349,7 +2317,6 @@
           <t>Ratio &amp; Proportion</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2375,8 +2342,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2407,7 +2372,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2438,7 +2402,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2504,7 +2467,6 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2607,7 +2569,6 @@
           <t>Heat</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2633,8 +2594,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2695,8 +2654,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2727,7 +2684,6 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2758,7 +2714,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2819,8 +2774,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2846,8 +2799,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2878,7 +2829,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2909,7 +2859,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2935,8 +2884,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2962,8 +2909,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2994,7 +2939,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3020,8 +2964,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3052,7 +2994,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3083,7 +3024,6 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3114,7 +3054,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3145,7 +3084,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3176,7 +3114,6 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3207,7 +3144,6 @@
           <t>Heat</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3233,8 +3169,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3265,7 +3199,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3331,7 +3264,6 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3362,7 +3294,6 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3388,7 +3319,6 @@
       <c r="G28" t="n">
         <v>2</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -3424,7 +3354,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3450,8 +3379,6 @@
       <c r="G30" t="n">
         <v>2</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3589,7 +3516,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3615,7 +3541,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -3651,7 +3576,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3682,7 +3606,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3708,8 +3631,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3775,7 +3696,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3841,7 +3761,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3867,7 +3786,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Visible improvement — the extra effort is showing results.</t>
@@ -3898,8 +3816,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3930,7 +3846,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3961,7 +3876,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3992,7 +3906,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4018,7 +3931,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -4054,7 +3966,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4115,7 +4026,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -4146,8 +4056,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4178,7 +4086,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4209,7 +4116,6 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4240,7 +4146,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4271,7 +4176,6 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4302,7 +4206,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4333,7 +4236,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4364,7 +4266,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4395,7 +4296,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4421,7 +4321,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -4492,7 +4391,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4590,7 +4488,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
@@ -4901,7 +4798,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -4932,7 +4828,6 @@
       <c r="G12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Noticeable drop in performance, please check in at home.</t>
@@ -5033,7 +4928,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Doing very well overall, minor slips in application-based questions.</t>
@@ -5099,7 +4993,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -5340,7 +5233,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Noticeable drop in performance, please check in at home.</t>
@@ -5511,7 +5403,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -5542,7 +5433,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
